--- a/docs/ig/ValueSet-dipag-rechnung-submit-modus-vs.xlsx
+++ b/docs/ig/ValueSet-dipag-rechnung-submit-modus-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Digitale Patientenrechnung Rechnung Type VS</t>
+    <t>Digitale Patientenrechnung Rechnung Submit Modus VS</t>
   </si>
   <si>
     <t>Status</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet für die Differenzierung von der Verarbeitungsmodi für $erchnung-submit</t>
+    <t>ValueSet für die Differenzierung der Verarbeitungsmodi für $invoice-submit</t>
   </si>
   <si>
     <t>Purpose</t>
